--- a/data/trans_dic/IP07_C15_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP07_C15_2023-Habitat-trans_dic.xlsx
@@ -490,18 +490,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio (tasa de respuesta: 92,89%)</t>
+          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio/instituto (tasa de respuesta: 92,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 13,04</t>
+          <t>2,96; 16,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 18,54</t>
+          <t>1,32; 11,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,34; 13,83</t>
+          <t>3,13; 13,54</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,36; 17,59</t>
+          <t>5,63; 19,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,33; 20,15</t>
+          <t>4,18; 17,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,19; 17,18</t>
+          <t>6,58; 15,88</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 18,27</t>
+          <t>1,73; 14,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 15,53</t>
+          <t>7,18; 25,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 14,39</t>
+          <t>5,41; 15,82</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,55%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,99; 29,48</t>
+          <t>9,69; 31,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,94; 30,83</t>
+          <t>8,55; 28,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,77; 25,59</t>
+          <t>11,5; 25,33</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,96; 15,25</t>
+          <t>7,5; 15,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,67; 16,06</t>
+          <t>8,34; 16,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,17; 14,19</t>
+          <t>8,61; 13,98</t>
         </is>
       </c>
     </row>
@@ -825,18 +825,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio (tasa de respuesta: 92,89%)</t>
+          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio/instituto (tasa de respuesta: 92,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>5415</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>415; 3991</t>
+          <t>1367; 7733</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1321; 8651</t>
+          <t>443; 4005</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2582; 10690</t>
+          <t>2497; 10802</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>5020</t>
+          <t>10923</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12189</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17209</t>
+          <t>16091</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2243; 9059</t>
+          <t>5708; 19584</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6467; 20593</t>
+          <t>2302; 9842</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11048; 26396</t>
+          <t>10301; 24839</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6449</t>
+          <t>2846</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>6595</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>9441</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1685; 12759</t>
+          <t>884; 7198</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>794; 7997</t>
+          <t>3370; 11975</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4140; 17460</t>
+          <t>5301; 15502</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>8260</t>
+          <t>8881</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9315</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17576</t>
+          <t>17463</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4677; 13805</t>
+          <t>4822; 15562</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4475; 15437</t>
+          <t>4254; 14109</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11409; 24795</t>
+          <t>11449; 25208</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21260</t>
+          <t>26465</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28374</t>
+          <t>21944</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49633</t>
+          <t>48409</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11854; 30319</t>
+          <t>18627; 37449</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19212; 40210</t>
+          <t>15458; 30076</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36702; 63756</t>
+          <t>37331; 60644</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP07_C15_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP07_C15_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio/instituto (tasa de respuesta: 92,89%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>8,26%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2,96; 16,73</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,32; 11,92</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3,13; 13,54</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>10,78%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>9,38%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>10,28%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>5,63; 19,32</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4,18; 17,86</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6,58; 15,88</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>5,57%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>14,05%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>9,63%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1,73; 14,09</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>7,18; 25,51</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>5,41; 15,82</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>17,85%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>17,24%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>17,55%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>9,69; 31,28</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>8,55; 28,34</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>11,5; 25,33</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>10,65%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>11,84%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>11,16%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>7,5; 15,08</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>8,34; 16,22</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8,61; 13,98</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.08256291184304876</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.04763796414222631</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.06786421929051711</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>3816</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5415</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.0295737250163303</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.01318308571570969</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.03128729163429755</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1367; 7733</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>443; 4005</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2497; 10802</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.16734080530533</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.119246102908498</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.1353709961384073</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.1077722414406193</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.09379255364525249</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.1028485378374862</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>10923</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5168</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>16091</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.05631850725034469</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.04177877727332158</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.06583794762689538</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>5708; 19584</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2302; 9842</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>10301; 24839</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.1932306438533143</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.1786106262756366</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.1587600327010735</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.05571869002148636</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1405116855071269</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.09632672277871383</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>2846</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>6595</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9441</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.01731024285675246</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.07180179669588778</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.05408796297551879</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>884; 7198</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3370; 11975</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5301; 15502</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.1409464641421173</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.2551273998137889</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.1581693781318325</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.1785229379528991</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1723922817626251</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1754566998729884</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>8881</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>8581</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>17463</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.09693526493687929</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.08546389998295273</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.1150333101358276</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>4822; 15562</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>4254; 14109</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>11449; 25208</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.3128155245002668</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.2834371187644373</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.2532784390312592</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.1065495886581912</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.1183621320570187</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1115983309592058</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>26465</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>21944</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>48409</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.07499174689289642</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.08337657299074749</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.08605981245352706</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>18627; 37449</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>15458; 30076</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>37331; 60644</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.1507715250547991</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.1622219595541471</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.1398032517546698</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio/instituto (tasa de respuesta: 92,89%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>3816</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>5415</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>1367</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>443</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>7733</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>4005</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>10802</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>10923</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>5168</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>16091</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>5708</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>2302</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>10301</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>19584</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>9842</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>24839</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>2846</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>6595</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>9441</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>884</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>3370</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>5301</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>7198</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>11975</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>15502</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>8881</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>8581</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>17463</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>4822</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>4254</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>11449</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>15562</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>14109</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>25208</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>26465</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>21944</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>48409</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>18627</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>15458</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>37331</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>37449</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>30076</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>60644</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>